--- a/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>花粉傳到雌蕊的過程是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>傳粉</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>種子</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>受精成功率高</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>體內受精</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>傳送</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>精卵結合的過程是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>果實</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>受精</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>胚珠</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>胚胎</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>植物受精後胚珠發育成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>種子</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>魚類與兩生類</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>雄蕊</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>胚</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>種子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>種子萌發長成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>種子</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>適當環境</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>風水動物</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>新植株</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>新株</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>產生花粉的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>種子</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>雄蕊</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>胚胎</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>雄性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>青蛙在水中受精屬？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>體外受精</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>胚珠</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>風水動物</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>水中</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>哺乳類多為哪種受精？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>體內受精</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>果實</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>體內</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>受精卵發育成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>胚胎</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>風水動物</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>體外受精</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>適當環境</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>胚</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>花的哪個部位接受花粉？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>果實</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>雌蕊(柱頭)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>雌蕊</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>受精後子房發育成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>果實</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>子房</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>果實</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>傳粉與受精差別？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>結合基因產生變異利適應</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>養分與適當環境保護</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>協助花粉傳送完成受精</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>傳粉傳花粉、受精精卵結合</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>種子常靠什麼傳播？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>風水動物</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>胚胎</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>受精成功率高</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>適當環境</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>傳播</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>魚類多為哪種受精？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>胚胎</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>適當環境</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>體外受精</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>水中</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>果實由什麼發育而來？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>子房</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>種子</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>雄蕊</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>果實</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>體內受精的優點？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>受精成功率高</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>體內受精</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>新植株</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>胚</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>雌蕊中含有？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>種子</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>胚珠</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>體內受精</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>雌性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>種子含有什麼可長成新株？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>風水動物</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>體外受精</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>魚類與兩生類</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>胚</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>胚</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>動物受精卵需什麼發育？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>胚</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>體內受精</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>適當環境</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>發育</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>蟲媒花常靠什麼傳粉？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>昆蟲</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>雌蕊(柱頭)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>傳粉</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>魚類與兩生類</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>媒介</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>體外受精常見於水生的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>胚珠</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>魚類與兩生類</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>果實</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>水中</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物5-3 動植物的生殖　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明開花植物從傳粉到新植株的完整過程？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>傳粉受精後胚珠成種子子房成果實種子萌發成新株</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>傳粉傳花粉、受精精卵結合</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>擴散分布減少競爭利繁衍</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>吸引昆蟲協助傳粉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>流程</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較體內與體外受精的優缺點？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>結合基因產生變異利適應</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>傳粉傳花粉、受精精卵結合</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>體內成功率高保護佳、體外量大但存活率低</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>吸引昆蟲協助傳粉</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>種子多樣傳播方式對植物的意義？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>擴散分布減少競爭利繁衍</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>傳粉傳花粉、受精精卵結合</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>結合基因產生變異利適應</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>傳播</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何有性生殖需雌雄生殖細胞結合？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>結合基因產生變異利適應</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>雄蕊產花粉雌蕊受粉發育種子</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>吸引昆蟲協助傳粉</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>花的構造如何配合生殖功能？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>雄蕊產花粉雌蕊受粉發育種子</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>協助花粉傳送完成受精</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>傳粉傳花粉、受精精卵結合</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>構造</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>動物胚胎發育需要哪些條件？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>養分與適當環境保護</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>吸引昆蟲協助傳粉</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>結合基因產生變異利適應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>傳粉媒介(蜂蝶風)對植物繁殖的重要？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>養分與適當環境保護</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>擴散分布減少競爭利繁衍</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>精卵在體內結合受保護</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>協助花粉傳送完成受精</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>媒介</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>果實對種子傳播的作用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>養分與適當環境保護</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>吸引昆蟲協助傳粉</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>吸引動物取食協助散播種子</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>果實</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>花色鮮豔與香氣對傳粉的意義？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>傳粉受精後胚珠成種子子房成果實種子萌發成新株</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>傳粉傳花粉、受精精卵結合</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>吸引昆蟲協助傳粉</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>吸引動物取食協助散播種子</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>吸引</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何體內受精受精率通常較高？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>精卵在體內結合受保護</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>體內成功率高保護佳、體外量大但存活率低</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>吸引動物取食協助散播種子</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>結合基因產生變異利適應</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>傳送</t>
+          <t>傳粉過程：花粉由雄蕊傳到雌蕊柱頭上的過程稱為傳粉，是受精前的準備步驟</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>結合過程：精細胞與卵細胞結合成一個新細胞的過程，稱為受精</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>種子</t>
+          <t>發育成種子：植物完成受精後，雌蕊內的胚珠會逐漸發育成種子</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>新株</t>
+          <t>萌發生長：種子在適當環境下萌發，胚會逐漸長成一株新的植物</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>雄性</t>
+          <t>花粉來源：花朵的雄蕊會產生花粉，花粉裡含有雄性生殖細胞</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>水中</t>
+          <t>水中受精：青蛙把精卵一起排到水中結合受精，這種方式稱為體外受精</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>體內</t>
+          <t>體內受精：哺乳類動物的精卵是在母體體內結合受精的，稱為體內受精</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>胚</t>
+          <t>發育成胚：受精卵經過細胞分裂與生長，會逐漸發育成胚胎</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>雌蕊</t>
+          <t>雌蕊：花粉落在雌蕊頂端的柱頭上，才能完成授粉，進一步發育出花粉管使精細胞到達胚珠</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>果實</t>
+          <t>果實：花朵受精後，子房會逐漸發育膨大形成果實，裡面的胚珠則發育成種子</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>兩階段區別：傳粉是花粉被傳送到雌蕊柱頭上，受精則是花粉裡的精細胞與卵細胞真正結合</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>傳播</t>
+          <t>多元傳播：種子常靠風吹、水流或動物攜帶等方式，被傳送到別的地方生長</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>水中</t>
+          <t>體外受精：多數魚類是把精子與卵子排到水中，在體外結合受精</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>果實</t>
+          <t>子房發育：植物受精後，包住胚珠的子房會逐漸發育膨大成果實</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>成功率高：體內受精在母體內進行，精卵不易流失，受精成功的機率比較高</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>雌性</t>
+          <t>雌蕊構造：雌蕊內部含有胚珠，胚珠受精後會發育成種子</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>胚</t>
+          <t>含有胚：種子裡含有胚，胚在適當條件下會萌發長成一株新的植物</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發育</t>
+          <t>需要環境：受精卵要在適當的溫度、養分等環境條件下，才能順利發育成新個體</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>媒介</t>
+          <t>媒介：蟲媒花通常有鮮豔的花色和香氣，用來吸引昆蟲當媒介，幫忙把花粉從一朵花帶到另一朵花</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>水中</t>
+          <t>水中：魚類和兩生類（如青蛙）大多把精細胞和卵細胞排到水中在體外結合，這種方式稱為體外受精，需要靠水作為媒介</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>流程</t>
+          <t>完整流程：花粉先被傳到雌蕊完成傳粉，受精後胚珠變成種子、子房變成果實，種子最後萌發長成新植株</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>兩種比較：體內受精精卵不易流失、成功率高又能保護胚胎，體外受精雖然產卵量大但容易被吃掉存活率較低</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>傳播</t>
+          <t>擴散意義：種子藉由不同方式傳播到遠處，能避免和母株搶奪養分陽光，有利族群繁衍擴散</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>產生變異：雌雄生殖細胞結合能讓兩方基因重新組合，產生的後代具有變異，有助於適應環境</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>構造</t>
+          <t>構造分工：花朵的雄蕊負責產生花粉，雌蕊負責接受花粉並在受精後發育成種子，兩者分工合作</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>發育條件：胚胎要順利發育成新個體，需要足夠的養分供應，以及適當溫度等環境的保護</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>媒介</t>
+          <t>傳粉媒介：蜜蜂蝴蝶或風能幫忙把花粉送到別朵花的雌蕊上，協助植物完成受精繁殖</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>果實</t>
+          <t>吸引取食：果實鮮豔美味能吸引動物取食，動物吃下後把種子帶到別處排出，幫助種子傳播</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>吸引</t>
+          <t>吸引：花朵演化出鮮豔的顏色與濃郁的香氣，主要目的是吸引昆蟲等傳粉者前來，順道幫忙把花粉傳播到其他花朵，提高授粉成功率</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：體內受精時精細胞和卵細胞在母體內部結合，不受外界環境（如水流、乾燥）的影響與威脅，因此受精成功的機率通常比體外受精高</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-3_三種難度測驗卷.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>果實</t>
+          <t>胚</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>胚珠</t>
+          <t>種子</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>胚胎</t>
+          <t>魚類與兩生類</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>新植株</t>
+          <t>胚胎</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>胚珠</t>
+          <t>風水動物</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>風水動物</t>
+          <t>受精成功率高</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>傳粉</t>
+          <t>適當環境</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>新植株</t>
+          <t>風水動物</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>果實</t>
+          <t>雄蕊</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>風水動物</t>
+          <t>昆蟲</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>體外受精</t>
+          <t>種子</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>適當環境</t>
+          <t>果實</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>胚胎</t>
+          <t>種子</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>受精</t>
+          <t>體內受精</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>適當環境</t>
+          <t>子房</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>體內受精</t>
+          <t>體外受精</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>新植株</t>
+          <t>風水動物</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>胚</t>
+          <t>昆蟲</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>傳粉</t>
+          <t>體外受精</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>種子</t>
+          <t>子房</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>體內受精</t>
+          <t>新植株</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>風水動物</t>
+          <t>雄蕊</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>體外受精</t>
+          <t>體內受精</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>魚類與兩生類</t>
+          <t>種子</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
